--- a/exam_plan.xlsx
+++ b/exam_plan.xlsx
@@ -3,14 +3,12 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="475" documentId="8_{93AFC7E6-B8D4-493B-98F6-B8A53D01F1B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{94DE2117-23F0-47D0-8FA0-89B6826B3A08}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{91FD25E7-8B89-470B-933A-E38CEF75A8F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="19440" windowHeight="11520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
-    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
-    <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -33,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="203" uniqueCount="128">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="65">
   <si>
     <t>IN</t>
   </si>
@@ -62,351 +60,165 @@
     <t>Alsheghri, Osman</t>
   </si>
   <si>
-    <t>202304782@post.au.dk</t>
-  </si>
-  <si>
     <t>Andersen, Stine Egebjerg</t>
   </si>
   <si>
-    <t>sea@bce.au.dk</t>
-  </si>
-  <si>
     <t>Arentoft, Cecilie Vad</t>
   </si>
   <si>
-    <t>202306250@post.au.dk</t>
-  </si>
-  <si>
     <t>Bertelsen, Sarah Sækmose</t>
   </si>
   <si>
-    <t>202305428@post.au.dk</t>
-  </si>
-  <si>
     <t>Carlsen, Emilie Weber</t>
   </si>
   <si>
-    <t>202305040@post.au.dk</t>
-  </si>
-  <si>
     <t>Degn, Ida Marie</t>
   </si>
   <si>
-    <t>imdegn@bce.au.dk</t>
-  </si>
-  <si>
     <t>Dokkedal, Marlene Lundby</t>
   </si>
   <si>
-    <t>202305904@post.au.dk</t>
-  </si>
-  <si>
     <t>Drasbek, Sigurd</t>
   </si>
   <si>
-    <t>202305569@post.au.dk</t>
-  </si>
-  <si>
     <t>Eskesen, Katja Abild</t>
   </si>
   <si>
-    <t>202305132@post.au.dk</t>
-  </si>
-  <si>
     <t>Fogh, Esben</t>
   </si>
   <si>
-    <t>202309340@post.au.dk</t>
-  </si>
-  <si>
     <t>Fuglsang, Frederik Kjeldbjerg</t>
   </si>
   <si>
-    <t>202307918@post.au.dk</t>
-  </si>
-  <si>
     <t>Grønbjerg, Helene Kaagh</t>
   </si>
   <si>
-    <t>202304538@post.au.dk</t>
-  </si>
-  <si>
     <t>Haddad, Paulus Majed Karayanni</t>
   </si>
   <si>
-    <t>202305826@post.au.dk</t>
-  </si>
-  <si>
     <t>Hallmann, Johanna Ravn</t>
   </si>
   <si>
-    <t>202306836@post.au.dk</t>
-  </si>
-  <si>
     <t>Harbo, Emilie Søgaard</t>
   </si>
   <si>
-    <t>202304882@post.au.dk</t>
-  </si>
-  <si>
     <t>Hedberg, Jonas Emil Ravn</t>
   </si>
   <si>
-    <t>202305646@post.au.dk</t>
-  </si>
-  <si>
     <t>Henriksen, Tina Ida Højgaard</t>
   </si>
   <si>
-    <t>202306187@post.au.dk</t>
-  </si>
-  <si>
     <t>Højrup, Frida Thykjær</t>
   </si>
   <si>
-    <t>202306001@post.au.dk</t>
-  </si>
-  <si>
     <t>Hvas, Smilla Gad</t>
   </si>
   <si>
-    <t>202307927@post.au.dk</t>
-  </si>
-  <si>
     <t>Hviid, Josefine</t>
   </si>
   <si>
-    <t>202305007@post.au.dk</t>
-  </si>
-  <si>
     <t>Ibsen, Sebastian Bøje</t>
   </si>
   <si>
-    <t>au754148@uni.au.dk</t>
-  </si>
-  <si>
     <t>Iraqi, Mariam Yahya</t>
   </si>
   <si>
-    <t>202305709@post.au.dk</t>
-  </si>
-  <si>
     <t>Jensen, Anne-Mette Hulegaard</t>
   </si>
   <si>
-    <t>202305309@post.au.dk</t>
-  </si>
-  <si>
     <t>Jessen, Laura Meilandt</t>
   </si>
   <si>
-    <t>202308609@post.au.dk</t>
-  </si>
-  <si>
     <t>Johannsen, Gustav Skovbo</t>
   </si>
   <si>
-    <t>202308325@post.au.dk</t>
-  </si>
-  <si>
     <t>Johansen, Clara Klit</t>
   </si>
   <si>
-    <t>202308298@post.au.dk</t>
-  </si>
-  <si>
     <t>Jungersen, Astrid</t>
   </si>
   <si>
-    <t>202308400@post.au.dk</t>
-  </si>
-  <si>
     <t>Kallesøe, Peter Hedegaard</t>
   </si>
   <si>
-    <t>201906299@post.au.dk</t>
-  </si>
-  <si>
     <t>Kampp, Lea</t>
   </si>
   <si>
-    <t>202309168@post.au.dk</t>
-  </si>
-  <si>
     <t>Kjeldsen, Jonas Steen</t>
   </si>
   <si>
-    <t>202308458@post.au.dk</t>
-  </si>
-  <si>
     <t>Klimat, Lucas</t>
   </si>
   <si>
-    <t>202309523@post.au.dk</t>
-  </si>
-  <si>
     <t>Krusborg, Emil Søbye</t>
   </si>
   <si>
-    <t>202306427@post.au.dk</t>
-  </si>
-  <si>
     <t>Kudsk, Magnus Højrup</t>
   </si>
   <si>
-    <t>202309386@post.au.dk</t>
-  </si>
-  <si>
     <t>Lambertsen, Iben Bach</t>
   </si>
   <si>
-    <t>202307592@post.au.dk</t>
-  </si>
-  <si>
     <t>Larsen, Emma Illum</t>
   </si>
   <si>
-    <t>202104233@post.au.dk</t>
-  </si>
-  <si>
     <t>Lejbølle, Christine</t>
   </si>
   <si>
-    <t>clej@bce.au.dk</t>
-  </si>
-  <si>
     <t>Leth, Philip Dokkedal</t>
   </si>
   <si>
-    <t>202004819@post.au.dk</t>
-  </si>
-  <si>
     <t>Mark, Johanne Warenu</t>
   </si>
   <si>
-    <t>jwm@au.dk</t>
-  </si>
-  <si>
     <t>Miltersen, Jonas Dalgaard</t>
   </si>
   <si>
-    <t>202306876@post.au.dk</t>
-  </si>
-  <si>
     <t>Nielsen, Rikke Kiilerich</t>
   </si>
   <si>
-    <t>202309435@post.au.dk</t>
-  </si>
-  <si>
     <t>Nilsen, Hedda Strand</t>
   </si>
   <si>
-    <t>202306203@post.au.dk</t>
-  </si>
-  <si>
     <t>Østergaard, Jonas</t>
   </si>
   <si>
-    <t>202305997@post.au.dk</t>
-  </si>
-  <si>
     <t>Pedersen, Anneline Østergaard</t>
   </si>
   <si>
-    <t>202308021@post.au.dk</t>
-  </si>
-  <si>
     <t>Poulsen, Kathrine Rumpelthiin</t>
   </si>
   <si>
-    <t>202207609@post.au.dk</t>
-  </si>
-  <si>
     <t>Priisholm, Jakob Ask</t>
   </si>
   <si>
-    <t>202204514@post.au.dk</t>
-  </si>
-  <si>
     <t>Rasmussen, Ida</t>
   </si>
   <si>
-    <t>202300163@post.au.dk</t>
-  </si>
-  <si>
     <t>Rasmussen, Viktor Juul</t>
   </si>
   <si>
-    <t>202308666@post.au.dk</t>
-  </si>
-  <si>
     <t>Rohde, Clara Askov</t>
   </si>
   <si>
-    <t>202306054@post.au.dk</t>
-  </si>
-  <si>
     <t>Roslev, Katrine Wirenfeldt</t>
   </si>
   <si>
-    <t>kwr@bce.au.dk</t>
-  </si>
-  <si>
     <t>Schmidt, Johanne Isaksen</t>
   </si>
   <si>
-    <t>202006371@post.au.dk</t>
-  </si>
-  <si>
     <t>Skovslund, Nanna Kjærgaard Nørgaard</t>
   </si>
   <si>
-    <t>202304816@post.au.dk</t>
-  </si>
-  <si>
     <t>Svendsen, Villads Lindberg</t>
   </si>
   <si>
-    <t>202306962@post.au.dk</t>
-  </si>
-  <si>
     <t>Thiesen, Johan Holtermann</t>
   </si>
   <si>
-    <t>202306720@post.au.dk</t>
-  </si>
-  <si>
     <t>Verbytska, Marharyta</t>
   </si>
   <si>
-    <t>202308517@post.au.dk</t>
-  </si>
-  <si>
-    <t>Student name</t>
-  </si>
-  <si>
-    <t>ID</t>
-  </si>
-  <si>
-    <t>Email</t>
-  </si>
-  <si>
-    <t>group</t>
-  </si>
-  <si>
-    <t>Clara Askov Rohde</t>
-  </si>
-  <si>
-    <t>request</t>
-  </si>
-  <si>
-    <t>early</t>
-  </si>
-  <si>
-    <t>late</t>
-  </si>
-  <si>
     <t>student</t>
   </si>
   <si>
@@ -414,41 +226,19 @@
   </si>
   <si>
     <t>PAUSE</t>
-  </si>
-  <si>
-    <t>H</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color theme="1"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color rgb="FF202122"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
     </font>
     <font>
       <b/>
@@ -459,21 +249,15 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="4">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -490,74 +274,22 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="20" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
     <xf numFmtId="16" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="16" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="16" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="16" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="16" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="20" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -573,72 +305,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>4</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>152400</xdr:colOff>
-      <xdr:row>4</xdr:row>
-      <xdr:rowOff>152400</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="19" name="Picture 18" descr="Ida Rasmussen is online">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F02E70AD-B67B-552C-0DEB-21B08BD3F1C6}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
-          <a:extLst>
-            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
-              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
-            </a:ext>
-          </a:extLst>
-        </a:blip>
-        <a:srcRect/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="0" y="33061275"/>
-          <a:ext cx="152400" cy="152400"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:extLst>
-          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
-            </a14:hiddenFill>
-          </a:ext>
-        </a:extLst>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -977,36 +643,36 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A1" s="4" t="s">
+      <c r="A1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="B1" s="4" t="s">
-        <v>125</v>
-      </c>
-      <c r="C1" s="4" t="s">
-        <v>124</v>
-      </c>
-      <c r="D1" s="15" t="s">
+      <c r="B1" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="D1" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="E1" s="4" t="s">
+      <c r="E1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="F1" s="4"/>
-      <c r="G1" s="4"/>
-      <c r="H1" s="4"/>
-      <c r="I1" s="15"/>
-      <c r="J1" s="4"/>
-      <c r="K1" s="4"/>
-      <c r="L1" s="4"/>
-      <c r="M1" s="4"/>
-      <c r="N1" s="15"/>
-      <c r="O1" s="4"/>
-      <c r="P1" s="4"/>
-      <c r="Q1" s="4"/>
-      <c r="R1" s="4"/>
-      <c r="S1" s="15"/>
-      <c r="T1" s="4"/>
+      <c r="F1" s="3"/>
+      <c r="G1" s="3"/>
+      <c r="H1" s="3"/>
+      <c r="I1" s="4"/>
+      <c r="J1" s="3"/>
+      <c r="K1" s="3"/>
+      <c r="L1" s="3"/>
+      <c r="M1" s="3"/>
+      <c r="N1" s="4"/>
+      <c r="O1" s="3"/>
+      <c r="P1" s="3"/>
+      <c r="Q1" s="3"/>
+      <c r="R1" s="3"/>
+      <c r="S1" s="4"/>
+      <c r="T1" s="3"/>
       <c r="V1" t="s">
         <v>3</v>
       </c>
@@ -1018,13 +684,13 @@
       </c>
     </row>
     <row r="2" spans="1:24" ht="21" x14ac:dyDescent="0.35">
-      <c r="A2" s="17">
+      <c r="A2" s="6">
         <v>45663</v>
       </c>
-      <c r="B2" s="17"/>
-      <c r="C2" s="17"/>
-      <c r="D2" s="17"/>
-      <c r="E2" s="17"/>
+      <c r="B2" s="6"/>
+      <c r="C2" s="6"/>
+      <c r="D2" s="6"/>
+      <c r="E2" s="6"/>
       <c r="I2" s="1"/>
       <c r="N2" s="1"/>
       <c r="S2" s="1"/>
@@ -1035,7 +701,7 @@
         <v>6</v>
       </c>
       <c r="B3" t="s">
-        <v>48</v>
+        <v>28</v>
       </c>
       <c r="C3">
         <v>1</v>
@@ -1061,7 +727,7 @@
         <v>6</v>
       </c>
       <c r="B4" t="s">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="C4">
         <v>2</v>
@@ -1087,7 +753,7 @@
         <v>6</v>
       </c>
       <c r="B5" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="C5">
         <v>3</v>
@@ -1113,7 +779,7 @@
         <v>6</v>
       </c>
       <c r="B6" t="s">
-        <v>66</v>
+        <v>37</v>
       </c>
       <c r="C6">
         <v>4</v>
@@ -1136,7 +802,7 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>70</v>
+        <v>39</v>
       </c>
       <c r="C7">
         <v>5</v>
@@ -1159,7 +825,7 @@
         <v>4</v>
       </c>
       <c r="B8" t="s">
-        <v>102</v>
+        <v>55</v>
       </c>
       <c r="C8">
         <v>6</v>
@@ -1182,7 +848,7 @@
         <v>4</v>
       </c>
       <c r="B9" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="C9">
         <v>7</v>
@@ -1202,10 +868,10 @@
     </row>
     <row r="10" spans="1:24" x14ac:dyDescent="0.25">
       <c r="B10" t="s">
-        <v>126</v>
+        <v>64</v>
       </c>
       <c r="C10" t="s">
-        <v>126</v>
+        <v>64</v>
       </c>
       <c r="D10" s="2">
         <v>0.49652777777777779</v>
@@ -1225,7 +891,7 @@
         <v>4</v>
       </c>
       <c r="B11" t="s">
-        <v>40</v>
+        <v>24</v>
       </c>
       <c r="C11">
         <v>8</v>
@@ -1248,7 +914,7 @@
         <v>4</v>
       </c>
       <c r="B12" t="s">
-        <v>64</v>
+        <v>36</v>
       </c>
       <c r="C12">
         <v>9</v>
@@ -1271,7 +937,7 @@
         <v>3</v>
       </c>
       <c r="B13" t="s">
-        <v>44</v>
+        <v>26</v>
       </c>
       <c r="C13">
         <v>10</v>
@@ -1294,7 +960,7 @@
         <v>3</v>
       </c>
       <c r="B14" t="s">
-        <v>52</v>
+        <v>30</v>
       </c>
       <c r="C14">
         <v>11</v>
@@ -1317,7 +983,7 @@
         <v>3</v>
       </c>
       <c r="B15" t="s">
-        <v>54</v>
+        <v>31</v>
       </c>
       <c r="C15">
         <v>12</v>
@@ -1338,7 +1004,7 @@
         <v>3</v>
       </c>
       <c r="B16" t="s">
-        <v>74</v>
+        <v>41</v>
       </c>
       <c r="C16">
         <v>13</v>
@@ -1359,7 +1025,7 @@
         <v>3</v>
       </c>
       <c r="B17" t="s">
-        <v>106</v>
+        <v>57</v>
       </c>
       <c r="C17">
         <v>14</v>
@@ -1376,13 +1042,13 @@
       <c r="O17" s="2"/>
     </row>
     <row r="18" spans="1:15" ht="21" x14ac:dyDescent="0.35">
-      <c r="A18" s="17">
+      <c r="A18" s="6">
         <v>45664</v>
       </c>
-      <c r="B18" s="17"/>
-      <c r="C18" s="17"/>
-      <c r="D18" s="17"/>
-      <c r="E18" s="17"/>
+      <c r="B18" s="6"/>
+      <c r="C18" s="6"/>
+      <c r="D18" s="6"/>
+      <c r="E18" s="6"/>
       <c r="F18" s="2"/>
       <c r="G18" s="2"/>
       <c r="H18" s="2"/>
@@ -1392,7 +1058,7 @@
         <v>1</v>
       </c>
       <c r="B19" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C19">
         <v>15</v>
@@ -1412,7 +1078,7 @@
         <v>1</v>
       </c>
       <c r="B20" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="C20">
         <v>16</v>
@@ -1432,7 +1098,7 @@
         <v>1</v>
       </c>
       <c r="B21" t="s">
-        <v>88</v>
+        <v>48</v>
       </c>
       <c r="C21">
         <v>17</v>
@@ -1445,16 +1111,14 @@
       </c>
       <c r="F21" s="2"/>
       <c r="G21" s="2"/>
-      <c r="H21" s="2" t="s">
-        <v>127</v>
-      </c>
+      <c r="H21" s="2"/>
     </row>
     <row r="22" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>1</v>
       </c>
       <c r="B22" t="s">
-        <v>98</v>
+        <v>53</v>
       </c>
       <c r="C22">
         <v>18</v>
@@ -1474,7 +1138,7 @@
         <v>1</v>
       </c>
       <c r="B23" t="s">
-        <v>104</v>
+        <v>56</v>
       </c>
       <c r="C23">
         <v>19</v>
@@ -1494,7 +1158,7 @@
         <v>2</v>
       </c>
       <c r="B24" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C24">
         <v>20</v>
@@ -1514,7 +1178,7 @@
         <v>2</v>
       </c>
       <c r="B25" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="C25">
         <v>21</v>
@@ -1531,10 +1195,10 @@
     </row>
     <row r="26" spans="1:15" x14ac:dyDescent="0.25">
       <c r="B26" t="s">
-        <v>126</v>
+        <v>64</v>
       </c>
       <c r="C26" t="s">
-        <v>126</v>
+        <v>64</v>
       </c>
       <c r="D26" s="2">
         <v>0.49652777777777779</v>
@@ -1551,7 +1215,7 @@
         <v>2</v>
       </c>
       <c r="B27" t="s">
-        <v>60</v>
+        <v>34</v>
       </c>
       <c r="C27">
         <v>22</v>
@@ -1571,7 +1235,7 @@
         <v>2</v>
       </c>
       <c r="B28" t="s">
-        <v>94</v>
+        <v>51</v>
       </c>
       <c r="C28">
         <v>23</v>
@@ -1591,7 +1255,7 @@
         <v>5</v>
       </c>
       <c r="B29" t="s">
-        <v>34</v>
+        <v>21</v>
       </c>
       <c r="C29">
         <v>24</v>
@@ -1611,7 +1275,7 @@
         <v>5</v>
       </c>
       <c r="B30" t="s">
-        <v>36</v>
+        <v>22</v>
       </c>
       <c r="C30">
         <v>25</v>
@@ -1631,7 +1295,7 @@
         <v>5</v>
       </c>
       <c r="B31" t="s">
-        <v>82</v>
+        <v>45</v>
       </c>
       <c r="C31">
         <v>26</v>
@@ -1651,7 +1315,7 @@
         <v>5</v>
       </c>
       <c r="B32" t="s">
-        <v>86</v>
+        <v>47</v>
       </c>
       <c r="C32">
         <v>27</v>
@@ -1671,7 +1335,7 @@
         <v>5</v>
       </c>
       <c r="B33" t="s">
-        <v>92</v>
+        <v>50</v>
       </c>
       <c r="C33">
         <v>28</v>
@@ -1687,13 +1351,13 @@
       <c r="H33" s="2"/>
     </row>
     <row r="34" spans="1:8" ht="21" x14ac:dyDescent="0.25">
-      <c r="A34" s="16">
+      <c r="A34" s="5">
         <v>45665</v>
       </c>
-      <c r="B34" s="16"/>
-      <c r="C34" s="16"/>
-      <c r="D34" s="16"/>
-      <c r="E34" s="16"/>
+      <c r="B34" s="5"/>
+      <c r="C34" s="5"/>
+      <c r="D34" s="5"/>
+      <c r="E34" s="5"/>
       <c r="F34" s="2"/>
       <c r="G34" s="2"/>
       <c r="H34" s="2"/>
@@ -1703,7 +1367,7 @@
         <v>8</v>
       </c>
       <c r="B35" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C35">
         <v>29</v>
@@ -1723,7 +1387,7 @@
         <v>8</v>
       </c>
       <c r="B36" t="s">
-        <v>42</v>
+        <v>25</v>
       </c>
       <c r="C36">
         <v>30</v>
@@ -1743,7 +1407,7 @@
         <v>8</v>
       </c>
       <c r="B37" t="s">
-        <v>112</v>
+        <v>60</v>
       </c>
       <c r="C37">
         <v>31</v>
@@ -1763,7 +1427,7 @@
         <v>10</v>
       </c>
       <c r="B38" t="s">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="C38">
         <v>32</v>
@@ -1783,7 +1447,7 @@
         <v>10</v>
       </c>
       <c r="B39" t="s">
-        <v>38</v>
+        <v>23</v>
       </c>
       <c r="C39">
         <v>33</v>
@@ -1803,7 +1467,7 @@
         <v>10</v>
       </c>
       <c r="B40" t="s">
-        <v>68</v>
+        <v>38</v>
       </c>
       <c r="C40">
         <v>34</v>
@@ -1823,7 +1487,7 @@
         <v>10</v>
       </c>
       <c r="B41" t="s">
-        <v>84</v>
+        <v>46</v>
       </c>
       <c r="C41">
         <v>35</v>
@@ -1840,10 +1504,10 @@
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B42" t="s">
-        <v>126</v>
+        <v>64</v>
       </c>
       <c r="C42" t="s">
-        <v>126</v>
+        <v>64</v>
       </c>
       <c r="D42" s="2">
         <v>0.49652777777777779</v>
@@ -1860,7 +1524,7 @@
         <v>11</v>
       </c>
       <c r="B43" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="C43">
         <v>36</v>
@@ -1880,7 +1544,7 @@
         <v>11</v>
       </c>
       <c r="B44" t="s">
-        <v>50</v>
+        <v>29</v>
       </c>
       <c r="C44">
         <v>37</v>
@@ -1900,7 +1564,7 @@
         <v>11</v>
       </c>
       <c r="B45" t="s">
-        <v>80</v>
+        <v>44</v>
       </c>
       <c r="C45">
         <v>38</v>
@@ -1920,7 +1584,7 @@
         <v>12</v>
       </c>
       <c r="B46" t="s">
-        <v>58</v>
+        <v>33</v>
       </c>
       <c r="C46">
         <v>39</v>
@@ -1940,7 +1604,7 @@
         <v>12</v>
       </c>
       <c r="B47" t="s">
-        <v>90</v>
+        <v>49</v>
       </c>
       <c r="C47">
         <v>40</v>
@@ -1960,7 +1624,7 @@
         <v>12</v>
       </c>
       <c r="B48" t="s">
-        <v>100</v>
+        <v>54</v>
       </c>
       <c r="C48">
         <v>41</v>
@@ -1980,7 +1644,7 @@
         <v>12</v>
       </c>
       <c r="B49" t="s">
-        <v>110</v>
+        <v>59</v>
       </c>
       <c r="C49">
         <v>42</v>
@@ -1996,13 +1660,13 @@
       <c r="H49" s="2"/>
     </row>
     <row r="50" spans="1:8" ht="21" x14ac:dyDescent="0.25">
-      <c r="A50" s="16">
+      <c r="A50" s="5">
         <v>45666</v>
       </c>
-      <c r="B50" s="16"/>
-      <c r="C50" s="16"/>
-      <c r="D50" s="16"/>
-      <c r="E50" s="16"/>
+      <c r="B50" s="5"/>
+      <c r="C50" s="5"/>
+      <c r="D50" s="5"/>
+      <c r="E50" s="5"/>
       <c r="F50" s="2"/>
       <c r="G50" s="2"/>
       <c r="H50" s="2"/>
@@ -2023,7 +1687,7 @@
       <c r="E51" s="2">
         <v>0.3923611111111111</v>
       </c>
-      <c r="F51" s="18"/>
+      <c r="F51" s="2"/>
       <c r="G51" s="2"/>
       <c r="H51" s="2"/>
     </row>
@@ -2032,7 +1696,7 @@
         <v>13</v>
       </c>
       <c r="B52" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="C52">
         <v>44</v>
@@ -2043,7 +1707,7 @@
       <c r="E52" s="2">
         <v>0.40972222222222221</v>
       </c>
-      <c r="F52" s="18"/>
+      <c r="F52" s="2"/>
       <c r="G52" s="2"/>
       <c r="H52" s="2"/>
     </row>
@@ -2052,7 +1716,7 @@
         <v>13</v>
       </c>
       <c r="B53" t="s">
-        <v>56</v>
+        <v>32</v>
       </c>
       <c r="C53">
         <v>45</v>
@@ -2063,7 +1727,7 @@
       <c r="E53" s="2">
         <v>0.42708333333333331</v>
       </c>
-      <c r="F53" s="18"/>
+      <c r="F53" s="2"/>
       <c r="G53" s="2"/>
       <c r="H53" s="2"/>
     </row>
@@ -2072,7 +1736,7 @@
         <v>13</v>
       </c>
       <c r="B54" t="s">
-        <v>72</v>
+        <v>40</v>
       </c>
       <c r="C54">
         <v>46</v>
@@ -2083,7 +1747,7 @@
       <c r="E54" s="2">
         <v>0.44444444444444442</v>
       </c>
-      <c r="F54" s="18"/>
+      <c r="F54" s="2"/>
       <c r="G54" s="2"/>
       <c r="H54" s="2"/>
     </row>
@@ -2092,7 +1756,7 @@
         <v>7</v>
       </c>
       <c r="B55" t="s">
-        <v>114</v>
+        <v>61</v>
       </c>
       <c r="C55">
         <v>47</v>
@@ -2103,7 +1767,7 @@
       <c r="E55" s="2">
         <v>0.46180555555555552</v>
       </c>
-      <c r="F55" s="18"/>
+      <c r="F55" s="2"/>
       <c r="G55" s="2"/>
       <c r="H55" s="2"/>
     </row>
@@ -2112,7 +1776,7 @@
         <v>7</v>
       </c>
       <c r="B56" t="s">
-        <v>96</v>
+        <v>52</v>
       </c>
       <c r="C56">
         <v>48</v>
@@ -2132,7 +1796,7 @@
         <v>7</v>
       </c>
       <c r="B57" t="s">
-        <v>76</v>
+        <v>42</v>
       </c>
       <c r="C57">
         <v>49</v>
@@ -2149,10 +1813,10 @@
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B58" t="s">
-        <v>126</v>
+        <v>64</v>
       </c>
       <c r="C58" t="s">
-        <v>126</v>
+        <v>64</v>
       </c>
       <c r="D58" s="2">
         <v>0.49652777777777779</v>
@@ -2169,7 +1833,7 @@
         <v>7</v>
       </c>
       <c r="B59" t="s">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="C59">
         <v>50</v>
@@ -2189,7 +1853,7 @@
         <v>7</v>
       </c>
       <c r="B60" t="s">
-        <v>62</v>
+        <v>35</v>
       </c>
       <c r="C60">
         <v>51</v>
@@ -2209,7 +1873,7 @@
         <v>9</v>
       </c>
       <c r="B61" t="s">
-        <v>46</v>
+        <v>27</v>
       </c>
       <c r="C61">
         <v>52</v>
@@ -2226,7 +1890,7 @@
         <v>9</v>
       </c>
       <c r="B62" t="s">
-        <v>78</v>
+        <v>43</v>
       </c>
       <c r="C62">
         <v>53</v>
@@ -2243,7 +1907,7 @@
         <v>9</v>
       </c>
       <c r="B63" t="s">
-        <v>108</v>
+        <v>58</v>
       </c>
       <c r="C63">
         <v>54</v>
@@ -2287,926 +1951,22 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5E914F28-9C5D-4EAB-9E34-365BFFDCA2BA}">
-  <dimension ref="A1:E56"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="33.85546875" style="3" customWidth="1"/>
-    <col min="2" max="2" width="24.42578125" customWidth="1"/>
-    <col min="3" max="3" width="43.28515625" customWidth="1"/>
-    <col min="11" max="11" width="17.5703125" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1" s="8" t="s">
-        <v>116</v>
-      </c>
-      <c r="B1" s="9" t="s">
-        <v>117</v>
-      </c>
-      <c r="C1" s="9" t="s">
-        <v>118</v>
-      </c>
-      <c r="D1" s="7" t="s">
-        <v>119</v>
-      </c>
-      <c r="E1" s="7" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A2" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="B2" s="6">
-        <v>748531</v>
-      </c>
-      <c r="C2" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="D2" s="7">
-        <v>1</v>
-      </c>
-      <c r="E2" s="7"/>
-    </row>
-    <row r="3" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A3" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="B3" s="6">
-        <v>717698</v>
-      </c>
-      <c r="C3" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="D3" s="7">
-        <v>1</v>
-      </c>
-      <c r="E3" s="7"/>
-    </row>
-    <row r="4" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A4" s="5" t="s">
-        <v>88</v>
-      </c>
-      <c r="B4" s="6">
-        <v>736793</v>
-      </c>
-      <c r="C4" s="6" t="s">
-        <v>89</v>
-      </c>
-      <c r="D4" s="7">
-        <v>1</v>
-      </c>
-      <c r="E4" s="7"/>
-    </row>
-    <row r="5" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A5" s="5" t="s">
-        <v>98</v>
-      </c>
-      <c r="B5" s="6">
-        <v>738609</v>
-      </c>
-      <c r="C5" s="6" t="s">
-        <v>99</v>
-      </c>
-      <c r="D5" s="7">
-        <v>1</v>
-      </c>
-      <c r="E5" s="7"/>
-    </row>
-    <row r="6" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A6" s="5" t="s">
-        <v>104</v>
-      </c>
-      <c r="B6" s="6">
-        <v>753302</v>
-      </c>
-      <c r="C6" s="6" t="s">
-        <v>105</v>
-      </c>
-      <c r="D6" s="7">
-        <v>1</v>
-      </c>
-      <c r="E6" s="7"/>
-    </row>
-    <row r="7" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A7" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="B7" s="6">
-        <v>754264</v>
-      </c>
-      <c r="C7" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="D7" s="7">
-        <v>2</v>
-      </c>
-      <c r="E7" s="7"/>
-    </row>
-    <row r="8" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A8" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="B8" s="6">
-        <v>742002</v>
-      </c>
-      <c r="C8" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="D8" s="7">
-        <v>2</v>
-      </c>
-      <c r="E8" s="7"/>
-    </row>
-    <row r="9" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A9" s="5" t="s">
-        <v>60</v>
-      </c>
-      <c r="B9" s="6">
-        <v>738429</v>
-      </c>
-      <c r="C9" s="6" t="s">
-        <v>61</v>
-      </c>
-      <c r="D9" s="7">
-        <v>2</v>
-      </c>
-      <c r="E9" s="7"/>
-    </row>
-    <row r="10" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A10" s="5" t="s">
-        <v>94</v>
-      </c>
-      <c r="B10" s="6">
-        <v>729565</v>
-      </c>
-      <c r="C10" s="6" t="s">
-        <v>95</v>
-      </c>
-      <c r="D10" s="7">
-        <v>2</v>
-      </c>
-      <c r="E10" s="7"/>
-    </row>
-    <row r="11" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A11" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="B11" s="6">
-        <v>753293</v>
-      </c>
-      <c r="C11" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="D11" s="7">
-        <v>3</v>
-      </c>
-      <c r="E11" s="7" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A12" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="B12" s="6">
-        <v>751127</v>
-      </c>
-      <c r="C12" s="6" t="s">
-        <v>53</v>
-      </c>
-      <c r="D12" s="7">
-        <v>3</v>
-      </c>
-      <c r="E12" s="7" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A13" s="5" t="s">
-        <v>54</v>
-      </c>
-      <c r="B13" s="6">
-        <v>707434</v>
-      </c>
-      <c r="C13" s="6" t="s">
-        <v>55</v>
-      </c>
-      <c r="D13" s="7">
-        <v>3</v>
-      </c>
-      <c r="E13" s="7" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A14" s="5" t="s">
-        <v>74</v>
-      </c>
-      <c r="B14" s="6">
-        <v>755555</v>
-      </c>
-      <c r="C14" s="6" t="s">
-        <v>75</v>
-      </c>
-      <c r="D14" s="7">
-        <v>3</v>
-      </c>
-      <c r="E14" s="7" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A15" s="5" t="s">
-        <v>106</v>
-      </c>
-      <c r="B15" s="6">
-        <v>633620</v>
-      </c>
-      <c r="C15" s="6" t="s">
-        <v>107</v>
-      </c>
-      <c r="D15" s="7">
-        <v>3</v>
-      </c>
-      <c r="E15" s="7" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A16" s="5" t="s">
-        <v>102</v>
-      </c>
-      <c r="B16" s="6">
-        <v>752770</v>
-      </c>
-      <c r="C16" s="6" t="s">
-        <v>103</v>
-      </c>
-      <c r="D16" s="7">
-        <v>4</v>
-      </c>
-      <c r="E16" s="7"/>
-    </row>
-    <row r="17" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A17" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="B17" s="6">
-        <v>750523</v>
-      </c>
-      <c r="C17" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="D17" s="7">
-        <v>4</v>
-      </c>
-      <c r="E17" s="7"/>
-    </row>
-    <row r="18" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A18" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B18" s="6">
-        <v>750705</v>
-      </c>
-      <c r="C18" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="D18" s="7">
-        <v>4</v>
-      </c>
-      <c r="E18" s="7"/>
-    </row>
-    <row r="19" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A19" s="5" t="s">
-        <v>64</v>
-      </c>
-      <c r="B19" s="6">
-        <v>743259</v>
-      </c>
-      <c r="C19" s="6" t="s">
-        <v>65</v>
-      </c>
-      <c r="D19" s="7">
-        <v>4</v>
-      </c>
-      <c r="E19" s="7"/>
-    </row>
-    <row r="20" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A20" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="B20" s="6">
-        <v>750530</v>
-      </c>
-      <c r="C20" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="D20" s="7">
-        <v>5</v>
-      </c>
-      <c r="E20" s="7" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A21" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="B21" s="6">
-        <v>740452</v>
-      </c>
-      <c r="C21" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="D21" s="7">
-        <v>5</v>
-      </c>
-      <c r="E21" s="7" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A22" s="5" t="s">
-        <v>82</v>
-      </c>
-      <c r="B22" s="6">
-        <v>750666</v>
-      </c>
-      <c r="C22" s="6" t="s">
-        <v>83</v>
-      </c>
-      <c r="D22" s="7">
-        <v>5</v>
-      </c>
-      <c r="E22" s="7" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A23" s="5" t="s">
-        <v>86</v>
-      </c>
-      <c r="B23" s="6">
-        <v>753677</v>
-      </c>
-      <c r="C23" s="6" t="s">
-        <v>87</v>
-      </c>
-      <c r="D23" s="7">
-        <v>5</v>
-      </c>
-      <c r="E23" s="7" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A24" s="5" t="s">
-        <v>92</v>
-      </c>
-      <c r="B24" s="6">
-        <v>753678</v>
-      </c>
-      <c r="C24" s="6" t="s">
-        <v>93</v>
-      </c>
-      <c r="D24" s="7">
-        <v>5</v>
-      </c>
-      <c r="E24" s="7" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A25" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="B25" s="6">
-        <v>755322</v>
-      </c>
-      <c r="C25" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="D25" s="7">
-        <v>6</v>
-      </c>
-      <c r="E25" s="7" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A26" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="B26" s="6">
-        <v>740610</v>
-      </c>
-      <c r="C26" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="D26" s="7">
-        <v>6</v>
-      </c>
-      <c r="E26" s="7" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A27" s="5" t="s">
-        <v>48</v>
-      </c>
-      <c r="B27" s="6">
-        <v>754148</v>
-      </c>
-      <c r="C27" s="6" t="s">
-        <v>49</v>
-      </c>
-      <c r="D27" s="7">
-        <v>6</v>
-      </c>
-      <c r="E27" s="7" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A28" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="B28" s="6">
-        <v>754692</v>
-      </c>
-      <c r="C28" s="6" t="s">
-        <v>67</v>
-      </c>
-      <c r="D28" s="7">
-        <v>6</v>
-      </c>
-      <c r="E28" s="7" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A29" s="5" t="s">
-        <v>70</v>
-      </c>
-      <c r="B29" s="6">
-        <v>754000</v>
-      </c>
-      <c r="C29" s="6" t="s">
-        <v>71</v>
-      </c>
-      <c r="D29" s="7">
-        <v>6</v>
-      </c>
-      <c r="E29" s="7" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A30" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="B30" s="6">
-        <v>482962</v>
-      </c>
-      <c r="C30" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="D30" s="7">
-        <v>7</v>
-      </c>
-      <c r="E30" s="7"/>
-    </row>
-    <row r="31" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A31" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="B31" s="6">
-        <v>637507</v>
-      </c>
-      <c r="C31" s="6" t="s">
-        <v>63</v>
-      </c>
-      <c r="D31" s="7">
-        <v>7</v>
-      </c>
-      <c r="E31" s="7"/>
-    </row>
-    <row r="32" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A32" s="5" t="s">
-        <v>76</v>
-      </c>
-      <c r="B32" s="6">
-        <v>698675</v>
-      </c>
-      <c r="C32" s="6" t="s">
-        <v>77</v>
-      </c>
-      <c r="D32" s="7">
-        <v>7</v>
-      </c>
-      <c r="E32" s="7"/>
-    </row>
-    <row r="33" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A33" s="5" t="s">
-        <v>96</v>
-      </c>
-      <c r="B33" s="6">
-        <v>712648</v>
-      </c>
-      <c r="C33" s="6" t="s">
-        <v>97</v>
-      </c>
-      <c r="D33" s="7">
-        <v>7</v>
-      </c>
-      <c r="E33" s="7"/>
-    </row>
-    <row r="34" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A34" s="5" t="s">
-        <v>114</v>
-      </c>
-      <c r="B34" s="6">
-        <v>739738</v>
-      </c>
-      <c r="C34" s="6" t="s">
-        <v>115</v>
-      </c>
-      <c r="D34" s="7">
-        <v>7</v>
-      </c>
-      <c r="E34" s="7"/>
-    </row>
-    <row r="35" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A35" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="B35" s="6">
-        <v>747113</v>
-      </c>
-      <c r="C35" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="D35" s="7">
-        <v>8</v>
-      </c>
-      <c r="E35" s="7"/>
-    </row>
-    <row r="36" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A36" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B36" s="6">
-        <v>747971</v>
-      </c>
-      <c r="C36" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="D36" s="7">
-        <v>8</v>
-      </c>
-      <c r="E36" s="7"/>
-    </row>
-    <row r="37" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A37" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="B37" s="6">
-        <v>754558</v>
-      </c>
-      <c r="C37" s="6" t="s">
-        <v>47</v>
-      </c>
-      <c r="D37" s="7">
-        <v>9</v>
-      </c>
-      <c r="E37" s="7"/>
-    </row>
-    <row r="38" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A38" s="5" t="s">
-        <v>78</v>
-      </c>
-      <c r="B38" s="6">
-        <v>740614</v>
-      </c>
-      <c r="C38" s="6" t="s">
-        <v>79</v>
-      </c>
-      <c r="D38" s="7">
-        <v>9</v>
-      </c>
-      <c r="E38" s="7" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="A39" s="5" t="s">
-        <v>108</v>
-      </c>
-      <c r="B39" s="6">
-        <v>738113</v>
-      </c>
-      <c r="C39" s="6" t="s">
-        <v>109</v>
-      </c>
-      <c r="D39" s="7">
-        <v>9</v>
-      </c>
-      <c r="E39" s="7"/>
-    </row>
-    <row r="40" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A40" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="B40" s="6">
-        <v>743636</v>
-      </c>
-      <c r="C40" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="D40" s="7">
-        <v>10</v>
-      </c>
-      <c r="E40" s="7"/>
-    </row>
-    <row r="41" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A41" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B41" s="6">
-        <v>740046</v>
-      </c>
-      <c r="C41" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="D41" s="7">
-        <v>10</v>
-      </c>
-      <c r="E41" s="7"/>
-    </row>
-    <row r="42" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A42" s="5" t="s">
-        <v>68</v>
-      </c>
-      <c r="B42" s="6">
-        <v>748841</v>
-      </c>
-      <c r="C42" s="6" t="s">
-        <v>69</v>
-      </c>
-      <c r="D42" s="7">
-        <v>10</v>
-      </c>
-      <c r="E42" s="7"/>
-    </row>
-    <row r="43" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A43" s="5" t="s">
-        <v>84</v>
-      </c>
-      <c r="B43" s="6">
-        <v>746996</v>
-      </c>
-      <c r="C43" s="6" t="s">
-        <v>85</v>
-      </c>
-      <c r="D43" s="7">
-        <v>10</v>
-      </c>
-      <c r="E43" s="7"/>
-    </row>
-    <row r="44" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A44" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="B44" s="6">
-        <v>754872</v>
-      </c>
-      <c r="C44" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="D44" s="7">
-        <v>11</v>
-      </c>
-      <c r="E44" s="7"/>
-    </row>
-    <row r="45" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A45" s="5" t="s">
-        <v>50</v>
-      </c>
-      <c r="B45" s="6">
-        <v>706256</v>
-      </c>
-      <c r="C45" s="6" t="s">
-        <v>51</v>
-      </c>
-      <c r="D45" s="7">
-        <v>11</v>
-      </c>
-      <c r="E45" s="7"/>
-    </row>
-    <row r="46" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A46" s="5" t="s">
-        <v>80</v>
-      </c>
-      <c r="B46" s="6">
-        <v>650890</v>
-      </c>
-      <c r="C46" s="6" t="s">
-        <v>81</v>
-      </c>
-      <c r="D46" s="7">
-        <v>11</v>
-      </c>
-      <c r="E46" s="7"/>
-    </row>
-    <row r="47" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A47" s="5" t="s">
-        <v>58</v>
-      </c>
-      <c r="B47" s="6">
-        <v>750232</v>
-      </c>
-      <c r="C47" s="6" t="s">
-        <v>59</v>
-      </c>
-      <c r="D47" s="7">
-        <v>12</v>
-      </c>
-      <c r="E47" s="7"/>
-    </row>
-    <row r="48" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A48" s="5" t="s">
-        <v>90</v>
-      </c>
-      <c r="B48" s="6">
-        <v>736491</v>
-      </c>
-      <c r="C48" s="6" t="s">
-        <v>91</v>
-      </c>
-      <c r="D48" s="7">
-        <v>12</v>
-      </c>
-      <c r="E48" s="7"/>
-    </row>
-    <row r="49" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A49" s="5" t="s">
-        <v>100</v>
-      </c>
-      <c r="B49" s="6">
-        <v>754700</v>
-      </c>
-      <c r="C49" s="6" t="s">
-        <v>101</v>
-      </c>
-      <c r="D49" s="7">
-        <v>12</v>
-      </c>
-      <c r="E49" s="7"/>
-    </row>
-    <row r="50" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A50" s="5" t="s">
-        <v>110</v>
-      </c>
-      <c r="B50" s="6">
-        <v>754955</v>
-      </c>
-      <c r="C50" s="6" t="s">
-        <v>111</v>
-      </c>
-      <c r="D50" s="7">
-        <v>12</v>
-      </c>
-      <c r="E50" s="7"/>
-    </row>
-    <row r="51" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A51" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="B51" s="6">
-        <v>744249</v>
-      </c>
-      <c r="C51" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="D51" s="7">
-        <v>13</v>
-      </c>
-      <c r="E51" s="7"/>
-    </row>
-    <row r="52" spans="1:5" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A52" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="B52" s="6">
-        <v>755260</v>
-      </c>
-      <c r="C52" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="D52" s="7">
-        <v>13</v>
-      </c>
-      <c r="E52" s="7"/>
-    </row>
-    <row r="53" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A53" s="5" t="s">
-        <v>56</v>
-      </c>
-      <c r="B53" s="6">
-        <v>738337</v>
-      </c>
-      <c r="C53" s="6" t="s">
-        <v>57</v>
-      </c>
-      <c r="D53" s="7">
-        <v>13</v>
-      </c>
-      <c r="E53" s="7"/>
-    </row>
-    <row r="54" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A54" s="5" t="s">
-        <v>72</v>
-      </c>
-      <c r="B54" s="6">
-        <v>711809</v>
-      </c>
-      <c r="C54" s="6" t="s">
-        <v>73</v>
-      </c>
-      <c r="D54" s="10">
-        <v>13</v>
-      </c>
-      <c r="E54" s="7"/>
-    </row>
-    <row r="55" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A55" s="11" t="s">
-        <v>112</v>
-      </c>
-      <c r="B55" s="12">
-        <v>754488</v>
-      </c>
-      <c r="C55" s="12" t="s">
-        <v>113</v>
-      </c>
-      <c r="D55" s="13">
-        <v>8</v>
-      </c>
-      <c r="E55" s="14"/>
-    </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A56" s="4"/>
-      <c r="B56" s="4"/>
-      <c r="C56" s="4"/>
-      <c r="D56" s="4"/>
-      <c r="E56" s="4"/>
-    </row>
-  </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:E56">
-    <sortCondition ref="D2:D56"/>
-  </sortState>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
-</worksheet>
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<TemplafyFormConfiguration><![CDATA[{"formFields":[],"formDataEntries":[]}]]></TemplafyFormConfiguration>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E1598C11-B1D6-4E8C-8195-7BAB7802049C}">
-  <dimension ref="A1:B1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
-        <v>120</v>
-      </c>
-      <c r="B1">
-        <v>4</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <TemplafyTemplateConfiguration><![CDATA[{"transformationConfigurations":[],"templateName":"blankspreadsheet","templateDescription":"","enableDocumentContentUpdater":false,"version":"2.0"}]]></TemplafyTemplateConfiguration>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<TemplafyFormConfiguration><![CDATA[{"formFields":[],"formDataEntries":[]}]]></TemplafyFormConfiguration>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7408D0D6-C97A-426B-8466-DDDAA7A3F420}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{613AEFFE-C095-42A7-A0AC-5564FFC1D197}">
   <ds:schemaRefs/>
 </ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{613AEFFE-C095-42A7-A0AC-5564FFC1D197}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7408D0D6-C97A-426B-8466-DDDAA7A3F420}">
   <ds:schemaRefs/>
 </ds:datastoreItem>
 </file>
--- a/exam_plan.xlsx
+++ b/exam_plan.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{91FD25E7-8B89-470B-933A-E38CEF75A8F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="4" documentId="8_{91FD25E7-8B89-470B-933A-E38CEF75A8F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{363FDD0E-5B35-432D-8D53-470767D86575}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="19440" windowHeight="11520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -1275,7 +1275,7 @@
         <v>5</v>
       </c>
       <c r="B30" t="s">
-        <v>22</v>
+        <v>50</v>
       </c>
       <c r="C30">
         <v>25</v>
@@ -1335,7 +1335,7 @@
         <v>5</v>
       </c>
       <c r="B33" t="s">
-        <v>50</v>
+        <v>22</v>
       </c>
       <c r="C33">
         <v>28</v>
@@ -1347,7 +1347,6 @@
         <v>0.66319444444444475</v>
       </c>
       <c r="F33" s="2"/>
-      <c r="G33" s="2"/>
       <c r="H33" s="2"/>
     </row>
     <row r="34" spans="1:8" ht="21" x14ac:dyDescent="0.25">

--- a/exam_plan.xlsx
+++ b/exam_plan.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="4" documentId="8_{91FD25E7-8B89-470B-933A-E38CEF75A8F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{363FDD0E-5B35-432D-8D53-470767D86575}"/>
+  <xr:revisionPtr revIDLastSave="8" documentId="8_{91FD25E7-8B89-470B-933A-E38CEF75A8F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9B958DB5-DE02-4F48-979F-A0F048AFE4DE}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="19440" windowHeight="11520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -1889,7 +1889,7 @@
         <v>9</v>
       </c>
       <c r="B62" t="s">
-        <v>43</v>
+        <v>58</v>
       </c>
       <c r="C62">
         <v>53</v>
@@ -1906,7 +1906,7 @@
         <v>9</v>
       </c>
       <c r="B63" t="s">
-        <v>58</v>
+        <v>43</v>
       </c>
       <c r="C63">
         <v>54</v>
@@ -1951,21 +1951,21 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<TemplafyTemplateConfiguration><![CDATA[{"transformationConfigurations":[],"templateName":"blankspreadsheet","templateDescription":"","enableDocumentContentUpdater":false,"version":"2.0"}]]></TemplafyTemplateConfiguration>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <TemplafyFormConfiguration><![CDATA[{"formFields":[],"formDataEntries":[]}]]></TemplafyFormConfiguration>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<TemplafyTemplateConfiguration><![CDATA[{"transformationConfigurations":[],"templateName":"blankspreadsheet","templateDescription":"","enableDocumentContentUpdater":false,"version":"2.0"}]]></TemplafyTemplateConfiguration>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{613AEFFE-C095-42A7-A0AC-5564FFC1D197}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7408D0D6-C97A-426B-8466-DDDAA7A3F420}">
   <ds:schemaRefs/>
 </ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7408D0D6-C97A-426B-8466-DDDAA7A3F420}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{613AEFFE-C095-42A7-A0AC-5564FFC1D197}">
   <ds:schemaRefs/>
 </ds:datastoreItem>
 </file>